--- a/scra/scra_pymt_history_from_2021.xlsx
+++ b/scra/scra_pymt_history_from_2021.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$99</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -1386,7 +1386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q117"/>
@@ -1440,7 +1440,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1481,7 +1481,7 @@
       <c r="P2" s="11"/>
       <c r="Q2" s="12"/>
     </row>
-    <row r="3" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" s="13" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <f t="shared" ref="A3:A34" si="0">A2+1</f>
         <v>2</v>
@@ -1525,7 +1525,7 @@
       <c r="P3" s="11"/>
       <c r="Q3" s="12"/>
     </row>
-    <row r="4" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" s="13" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1568,7 +1568,7 @@
       <c r="O4" s="11"/>
       <c r="Q4" s="12"/>
     </row>
-    <row r="5" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1681,8 +1681,8 @@
       <c r="J7" s="8">
         <v>1500</v>
       </c>
-      <c r="K7" s="36">
-        <v>0</v>
+      <c r="K7" s="18">
+        <v>2500</v>
       </c>
       <c r="L7" s="49" t="s">
         <v>169</v>
@@ -1807,8 +1807,8 @@
       <c r="J10" s="9">
         <v>7500</v>
       </c>
-      <c r="K10" s="36">
-        <v>0</v>
+      <c r="K10" s="18">
+        <v>7500</v>
       </c>
       <c r="L10" s="9"/>
       <c r="M10" s="10"/>
@@ -1817,7 +1817,7 @@
       <c r="P10" s="11"/>
       <c r="Q10" s="12"/>
     </row>
-    <row r="11" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="47">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1859,7 +1859,7 @@
       <c r="P11" s="11"/>
       <c r="Q11" s="12"/>
     </row>
-    <row r="12" spans="1:17" s="13" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" s="13" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1903,7 +1903,7 @@
       <c r="P12" s="11"/>
       <c r="Q12" s="12"/>
     </row>
-    <row r="13" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" s="13" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1991,7 +1991,7 @@
       <c r="P14" s="11"/>
       <c r="Q14" s="12"/>
     </row>
-    <row r="15" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" s="13" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="51">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2033,7 +2033,7 @@
       <c r="P15" s="11"/>
       <c r="Q15" s="12"/>
     </row>
-    <row r="16" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="51">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2261,7 +2261,7 @@
       <c r="P21" s="11"/>
       <c r="Q21" s="12"/>
     </row>
-    <row r="22" spans="1:17" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" s="13" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2379,8 +2379,8 @@
       <c r="J24" s="18">
         <v>7500</v>
       </c>
-      <c r="K24" s="36">
-        <v>0</v>
+      <c r="K24" s="18">
+        <v>7500</v>
       </c>
       <c r="L24" s="9"/>
       <c r="M24" s="10"/>
@@ -2389,7 +2389,7 @@
       <c r="P24" s="11"/>
       <c r="Q24" s="12"/>
     </row>
-    <row r="25" spans="1:17" s="13" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" s="13" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2515,7 +2515,7 @@
       <c r="P27" s="11"/>
       <c r="Q27" s="12"/>
     </row>
-    <row r="28" spans="1:17" s="13" customFormat="1" ht="32.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" s="13" customFormat="1" ht="32.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2683,7 +2683,7 @@
       <c r="P31" s="11"/>
       <c r="Q31" s="12"/>
     </row>
-    <row r="32" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" s="13" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -2809,7 +2809,7 @@
       <c r="P34" s="11"/>
       <c r="Q34" s="12"/>
     </row>
-    <row r="35" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" s="13" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <f t="shared" ref="A35:A66" si="1">A34+1</f>
         <v>34</v>
@@ -2893,7 +2893,7 @@
       <c r="P36" s="11"/>
       <c r="Q36" s="12"/>
     </row>
-    <row r="37" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="51">
         <f t="shared" si="1"/>
         <v>36</v>
@@ -3091,7 +3091,7 @@
       <c r="P41" s="11"/>
       <c r="Q41" s="12"/>
     </row>
-    <row r="42" spans="1:17" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" s="13" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="55">
         <f t="shared" si="1"/>
         <v>41</v>
@@ -3241,8 +3241,8 @@
       <c r="J45" s="9">
         <v>7500</v>
       </c>
-      <c r="K45" s="36">
-        <v>0</v>
+      <c r="K45" s="18">
+        <v>2500</v>
       </c>
       <c r="L45" s="9" t="s">
         <v>196</v>
@@ -3589,7 +3589,7 @@
       <c r="P53" s="11"/>
       <c r="Q53" s="12"/>
     </row>
-    <row r="54" spans="1:17" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" s="13" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="47">
         <f t="shared" si="1"/>
         <v>53</v>
@@ -3631,7 +3631,7 @@
       <c r="P54" s="11"/>
       <c r="Q54" s="12"/>
     </row>
-    <row r="55" spans="1:17" s="13" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" s="13" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <f t="shared" si="1"/>
         <v>54</v>
@@ -3719,7 +3719,7 @@
       <c r="P56" s="11"/>
       <c r="Q56" s="12"/>
     </row>
-    <row r="57" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" s="13" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
         <f t="shared" si="1"/>
         <v>56</v>
@@ -3881,7 +3881,7 @@
       <c r="P61" s="11"/>
       <c r="Q61" s="12"/>
     </row>
-    <row r="62" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" s="13" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <f t="shared" si="1"/>
         <v>61</v>
@@ -3923,7 +3923,7 @@
       <c r="P62" s="11"/>
       <c r="Q62" s="12"/>
     </row>
-    <row r="63" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" s="13" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
         <f t="shared" si="1"/>
         <v>62</v>
@@ -3965,7 +3965,7 @@
       <c r="P63" s="11"/>
       <c r="Q63" s="12"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <f t="shared" si="1"/>
         <v>63</v>
@@ -4039,7 +4039,7 @@
       </c>
       <c r="L65" s="9"/>
     </row>
-    <row r="66" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="55">
         <f t="shared" si="1"/>
         <v>65</v>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="L68" s="24"/>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="46">
         <f t="shared" si="2"/>
         <v>68</v>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="L69" s="9"/>
     </row>
-    <row r="70" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <f t="shared" si="2"/>
         <v>69</v>
@@ -4256,8 +4256,8 @@
       <c r="J71" s="18">
         <v>10000</v>
       </c>
-      <c r="K71" s="36">
-        <v>0</v>
+      <c r="K71" s="18">
+        <v>10000</v>
       </c>
       <c r="L71" s="9"/>
     </row>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="L74" s="9"/>
     </row>
-    <row r="75" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
         <f t="shared" si="2"/>
         <v>74</v>
@@ -4399,7 +4399,7 @@
       </c>
       <c r="L75" s="9"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <f t="shared" si="2"/>
         <v>75</v>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="L82" s="42"/>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
         <f t="shared" si="2"/>
         <v>82</v>
@@ -4696,7 +4696,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
         <f t="shared" si="2"/>
         <v>84</v>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="L86" s="9"/>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
         <f t="shared" si="2"/>
         <v>86</v>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="L89" s="9"/>
     </row>
-    <row r="90" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
         <f t="shared" si="2"/>
         <v>89</v>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="L92" s="24"/>
     </row>
-    <row r="93" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
         <f t="shared" si="2"/>
         <v>92</v>
@@ -5173,7 +5173,7 @@
       </c>
       <c r="L97" s="9"/>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="5">
         <f t="shared" si="2"/>
         <v>97</v>
@@ -5206,7 +5206,7 @@
       </c>
       <c r="L98" s="9"/>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
         <f t="shared" si="2"/>
         <v>98</v>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="K103" s="32">
         <f>COUNTIFS(E2:E98, "House", K2:K98, "&lt;&gt;0")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="104" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="K104" s="32">
         <f>COUNTIFS(E2:E98, "Apartment", K2:K98, "&lt;&gt;0")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="K105" s="32">
         <f>COUNTIFS(E2:E98, "Ind. Apartment", K2:K98, "&lt;&gt;0")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="106" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="K110" s="32">
         <f>COUNTIFS(D2:D98, "1st Main", K2:K98, "&lt;&gt;0")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="111" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="K111" s="32">
         <f>COUNTIFS(D2:D98, "2nd Main", K2:K98, "&lt;&gt;0")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="K112" s="32">
         <f>COUNTIFS(D2:D98, "3rd Main", K2:K98, "&lt;&gt;0")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="113" spans="5:11" ht="18.75" x14ac:dyDescent="0.3">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="K113" s="32">
         <f>COUNTIFS(D2:D98, "1st Cross", K2:K98, "&lt;&gt;0")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="5:11" ht="18.75" x14ac:dyDescent="0.3">
@@ -5586,11 +5586,16 @@
       </c>
       <c r="K117" s="32">
         <f>COUNTIFS(D2:D98, "Seethammal Road", K2:K98, "&lt;&gt;0")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L98">
+  <autoFilter ref="A1:L99">
+    <filterColumn colId="10">
+      <filters>
+        <filter val="0.00"/>
+      </filters>
+    </filterColumn>
     <sortState ref="A2:J96">
       <sortCondition ref="D1:D96"/>
     </sortState>

--- a/scra/scra_pymt_history_from_2021.xlsx
+++ b/scra/scra_pymt_history_from_2021.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="207">
   <si>
     <t>S No</t>
   </si>
@@ -384,12 +384,6 @@
     <t>Sundararajan R</t>
   </si>
   <si>
-    <t>Suresh Ramaswamy</t>
-  </si>
-  <si>
-    <t>Kaushik Apartment</t>
-  </si>
-  <si>
     <t>U R Srinivasan</t>
   </si>
   <si>
@@ -805,6 +799,12 @@
   </si>
   <si>
     <t>8 First Main Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shantha </t>
+  </si>
+  <si>
+    <t>First payment in 2026</t>
   </si>
 </sst>
 </file>
@@ -1078,9 +1078,6 @@
     <xf numFmtId="2" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1106,6 +1103,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1386,7 +1384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q117"/>
@@ -1428,19 +1426,19 @@
         <v>7</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L1" s="24" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1481,7 +1479,7 @@
       <c r="P2" s="11"/>
       <c r="Q2" s="12"/>
     </row>
-    <row r="3" spans="1:17" s="13" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <f t="shared" ref="A3:A34" si="0">A2+1</f>
         <v>2</v>
@@ -1517,7 +1515,7 @@
         <v>7500</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="M3" s="10"/>
       <c r="N3" s="11"/>
@@ -1525,7 +1523,7 @@
       <c r="P3" s="11"/>
       <c r="Q3" s="12"/>
     </row>
-    <row r="4" spans="1:17" s="13" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1561,14 +1559,14 @@
         <v>2500</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="M4" s="10"/>
       <c r="N4" s="11"/>
       <c r="O4" s="11"/>
       <c r="Q4" s="12"/>
     </row>
-    <row r="5" spans="1:17" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1655,16 +1653,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>41</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F7" s="20">
         <v>0</v>
@@ -1684,8 +1682,8 @@
       <c r="K7" s="18">
         <v>2500</v>
       </c>
-      <c r="L7" s="49" t="s">
-        <v>169</v>
+      <c r="L7" s="48" t="s">
+        <v>167</v>
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="11"/>
@@ -1699,7 +1697,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>22</v>
@@ -1725,8 +1723,8 @@
       <c r="J8" s="9">
         <v>2500</v>
       </c>
-      <c r="K8" s="36">
-        <v>0</v>
+      <c r="K8" s="18">
+        <v>2500</v>
       </c>
       <c r="L8" s="9"/>
       <c r="M8" s="10"/>
@@ -1817,8 +1815,8 @@
       <c r="P10" s="11"/>
       <c r="Q10" s="12"/>
     </row>
-    <row r="11" spans="1:17" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="47">
+    <row r="11" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="46">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -1826,7 +1824,7 @@
         <v>91</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>23</v>
@@ -1859,16 +1857,16 @@
       <c r="P11" s="11"/>
       <c r="Q11" s="12"/>
     </row>
-    <row r="12" spans="1:17" s="13" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" s="13" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>23</v>
@@ -1895,7 +1893,7 @@
         <v>2500</v>
       </c>
       <c r="L12" s="24" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="11"/>
@@ -1903,13 +1901,13 @@
       <c r="P12" s="11"/>
       <c r="Q12" s="12"/>
     </row>
-    <row r="13" spans="1:17" s="13" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>20</v>
@@ -1939,7 +1937,7 @@
         <v>2500</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="M13" s="10"/>
       <c r="N13" s="11"/>
@@ -1983,7 +1981,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="25" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="M14" s="10"/>
       <c r="N14" s="11"/>
@@ -1991,34 +1989,34 @@
       <c r="P14" s="11"/>
       <c r="Q14" s="12"/>
     </row>
-    <row r="15" spans="1:17" s="13" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="51">
+    <row r="15" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="50">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B15" s="52" t="s">
-        <v>202</v>
-      </c>
-      <c r="C15" s="52" t="s">
-        <v>181</v>
-      </c>
-      <c r="D15" s="48" t="s">
+      <c r="B15" s="51" t="s">
+        <v>200</v>
+      </c>
+      <c r="C15" s="51" t="s">
+        <v>179</v>
+      </c>
+      <c r="D15" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="48" t="s">
-        <v>102</v>
+      <c r="E15" s="47" t="s">
+        <v>100</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="J15" s="9">
         <v>1500</v>
@@ -2033,22 +2031,22 @@
       <c r="P15" s="11"/>
       <c r="Q15" s="12"/>
     </row>
-    <row r="16" spans="1:17" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="51">
+    <row r="16" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="50">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" s="52" t="s">
-        <v>182</v>
-      </c>
-      <c r="C16" s="52" t="s">
-        <v>181</v>
-      </c>
-      <c r="D16" s="48" t="s">
+      <c r="B16" s="51" t="s">
+        <v>180</v>
+      </c>
+      <c r="C16" s="51" t="s">
+        <v>179</v>
+      </c>
+      <c r="D16" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="E16" s="48" t="s">
-        <v>102</v>
+      <c r="E16" s="47" t="s">
+        <v>100</v>
       </c>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
@@ -2068,21 +2066,21 @@
       <c r="Q16" s="12"/>
     </row>
     <row r="17" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="51">
+      <c r="A17" s="50">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="52" t="s">
-        <v>183</v>
-      </c>
-      <c r="C17" s="52" t="s">
+      <c r="B17" s="51" t="s">
         <v>181</v>
       </c>
-      <c r="D17" s="48" t="s">
+      <c r="C17" s="51" t="s">
+        <v>179</v>
+      </c>
+      <c r="D17" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="E17" s="48" t="s">
-        <v>102</v>
+      <c r="E17" s="47" t="s">
+        <v>100</v>
       </c>
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
@@ -2149,10 +2147,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>21</v>
@@ -2190,17 +2188,17 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B20" s="52" t="s">
-        <v>184</v>
-      </c>
-      <c r="C20" s="52" t="s">
-        <v>181</v>
-      </c>
-      <c r="D20" s="48" t="s">
+      <c r="B20" s="51" t="s">
+        <v>182</v>
+      </c>
+      <c r="C20" s="51" t="s">
+        <v>179</v>
+      </c>
+      <c r="D20" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="E20" s="48" t="s">
-        <v>102</v>
+      <c r="E20" s="47" t="s">
+        <v>100</v>
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
@@ -2212,7 +2210,7 @@
       <c r="K20" s="36">
         <v>0</v>
       </c>
-      <c r="L20" s="50"/>
+      <c r="L20" s="49"/>
       <c r="M20" s="10"/>
       <c r="N20" s="11"/>
       <c r="O20" s="11"/>
@@ -2249,7 +2247,7 @@
         <v>1500</v>
       </c>
       <c r="J21" s="18" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="K21" s="36">
         <v>0</v>
@@ -2261,7 +2259,7 @@
       <c r="P21" s="11"/>
       <c r="Q21" s="12"/>
     </row>
-    <row r="22" spans="1:17" s="13" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2297,7 +2295,7 @@
         <v>2500</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M22" s="10"/>
       <c r="N22" s="11"/>
@@ -2311,16 +2309,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>34</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F23" s="8">
         <v>0</v>
@@ -2353,10 +2351,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>34</v>
@@ -2389,22 +2387,22 @@
       <c r="P24" s="11"/>
       <c r="Q24" s="12"/>
     </row>
-    <row r="25" spans="1:17" s="13" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" s="13" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D25" s="7" t="s">
         <v>34</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F25" s="8">
         <v>0</v>
@@ -2437,10 +2435,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>34</v>
@@ -2463,8 +2461,8 @@
       <c r="J26" s="20">
         <v>0</v>
       </c>
-      <c r="K26" s="36">
-        <v>0</v>
+      <c r="K26" s="18">
+        <v>2500</v>
       </c>
       <c r="L26" s="9"/>
       <c r="M26" s="10"/>
@@ -2515,7 +2513,7 @@
       <c r="P27" s="11"/>
       <c r="Q27" s="12"/>
     </row>
-    <row r="28" spans="1:17" s="13" customFormat="1" ht="32.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" s="13" customFormat="1" ht="32.25" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2589,8 +2587,8 @@
       <c r="J29" s="9">
         <v>2500</v>
       </c>
-      <c r="K29" s="36">
-        <v>0</v>
+      <c r="K29" s="18">
+        <v>2500</v>
       </c>
       <c r="L29" s="9"/>
       <c r="M29" s="10"/>
@@ -2600,20 +2598,20 @@
       <c r="Q29" s="12"/>
     </row>
     <row r="30" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" s="47">
+      <c r="A30" s="46">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B30" s="52" t="s">
-        <v>185</v>
-      </c>
-      <c r="C30" s="52" t="s">
-        <v>186</v>
-      </c>
-      <c r="D30" s="48" t="s">
+      <c r="B30" s="51" t="s">
+        <v>183</v>
+      </c>
+      <c r="C30" s="51" t="s">
+        <v>184</v>
+      </c>
+      <c r="D30" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="E30" s="48"/>
+      <c r="E30" s="47"/>
       <c r="F30" s="8">
         <v>0</v>
       </c>
@@ -2645,10 +2643,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>17</v>
@@ -2671,11 +2669,11 @@
       <c r="J31" s="8">
         <v>5000</v>
       </c>
-      <c r="K31" s="36">
-        <v>0</v>
+      <c r="K31" s="18">
+        <v>2500</v>
       </c>
       <c r="L31" s="24" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M31" s="10"/>
       <c r="N31" s="11"/>
@@ -2683,22 +2681,22 @@
       <c r="P31" s="11"/>
       <c r="Q31" s="12"/>
     </row>
-    <row r="32" spans="1:17" s="13" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F32" s="8">
         <v>0</v>
@@ -2731,16 +2729,16 @@
         <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F33" s="8">
         <v>0</v>
@@ -2773,16 +2771,16 @@
         <v>33</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F34" s="8">
         <v>0</v>
@@ -2809,22 +2807,22 @@
       <c r="P34" s="11"/>
       <c r="Q34" s="12"/>
     </row>
-    <row r="35" spans="1:17" s="13" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <f t="shared" ref="A35:A66" si="1">A34+1</f>
         <v>34</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F35" s="8">
         <v>0</v>
@@ -2857,16 +2855,16 @@
         <v>35</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F36" s="8">
         <v>0</v>
@@ -2893,21 +2891,21 @@
       <c r="P36" s="11"/>
       <c r="Q36" s="12"/>
     </row>
-    <row r="37" spans="1:17" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="51">
+    <row r="37" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="50">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
-      <c r="B37" s="52" t="s">
-        <v>205</v>
-      </c>
-      <c r="C37" s="52" t="s">
-        <v>206</v>
-      </c>
-      <c r="D37" s="48" t="s">
+      <c r="B37" s="51" t="s">
+        <v>203</v>
+      </c>
+      <c r="C37" s="51" t="s">
+        <v>204</v>
+      </c>
+      <c r="D37" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="E37" s="48"/>
+      <c r="E37" s="47"/>
       <c r="F37" s="8">
         <v>0</v>
       </c>
@@ -2926,7 +2924,7 @@
       <c r="K37" s="18">
         <v>2500</v>
       </c>
-      <c r="L37" s="50"/>
+      <c r="L37" s="49"/>
       <c r="M37" s="10"/>
       <c r="N37" s="11"/>
       <c r="O37" s="11"/>
@@ -2969,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="L38" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="M38" s="10"/>
       <c r="N38" s="11"/>
@@ -3009,11 +3007,11 @@
       <c r="J39" s="18">
         <v>2500</v>
       </c>
-      <c r="K39" s="36">
-        <v>0</v>
+      <c r="K39" s="18">
+        <v>2500</v>
       </c>
       <c r="L39" s="9" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="M39" s="10"/>
       <c r="N39" s="11"/>
@@ -3057,7 +3055,7 @@
         <v>0</v>
       </c>
       <c r="L40" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M40" s="10"/>
       <c r="N40" s="11"/>
@@ -3065,47 +3063,55 @@
       <c r="P40" s="11"/>
       <c r="Q40" s="12"/>
     </row>
-    <row r="41" spans="1:17" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="39">
+    <row r="41" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A41" s="56">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="B41" s="41" t="s">
-        <v>156</v>
-      </c>
-      <c r="C41" s="40"/>
-      <c r="D41" s="41"/>
-      <c r="E41" s="41"/>
-      <c r="F41" s="38"/>
-      <c r="G41" s="38"/>
-      <c r="H41" s="43"/>
-      <c r="I41" s="43"/>
-      <c r="J41" s="43"/>
-      <c r="K41" s="36">
-        <v>0</v>
-      </c>
-      <c r="L41" s="42"/>
+      <c r="B41" s="56" t="s">
+        <v>205</v>
+      </c>
+      <c r="C41" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" s="56" t="s">
+        <v>100</v>
+      </c>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="18">
+        <v>1500</v>
+      </c>
+      <c r="L41" s="9" t="s">
+        <v>206</v>
+      </c>
       <c r="M41" s="10"/>
       <c r="N41" s="11"/>
       <c r="O41" s="11"/>
       <c r="P41" s="11"/>
       <c r="Q41" s="12"/>
     </row>
-    <row r="42" spans="1:17" s="13" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="55">
+    <row r="42" spans="1:17" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="54">
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
-      <c r="B42" s="55" t="s">
-        <v>203</v>
-      </c>
-      <c r="C42" s="54" t="s">
-        <v>204</v>
-      </c>
-      <c r="D42" s="55" t="s">
+      <c r="B42" s="54" t="s">
+        <v>201</v>
+      </c>
+      <c r="C42" s="53" t="s">
+        <v>202</v>
+      </c>
+      <c r="D42" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="E42" s="55" t="s">
+      <c r="E42" s="54" t="s">
         <v>12</v>
       </c>
       <c r="F42" s="20"/>
@@ -3245,7 +3251,7 @@
         <v>2500</v>
       </c>
       <c r="L45" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M45" s="10"/>
       <c r="N45" s="11"/>
@@ -3262,7 +3268,7 @@
         <v>78</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>31</v>
@@ -3285,8 +3291,8 @@
       <c r="J46" s="9">
         <v>2500</v>
       </c>
-      <c r="K46" s="36">
-        <v>0</v>
+      <c r="K46" s="18">
+        <v>2500</v>
       </c>
       <c r="L46" s="9"/>
       <c r="M46" s="10"/>
@@ -3385,10 +3391,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D49" s="7" t="s">
         <v>31</v>
@@ -3427,10 +3433,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>31</v>
@@ -3469,7 +3475,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>30</v>
@@ -3495,8 +3501,8 @@
       <c r="J51" s="18">
         <v>7500</v>
       </c>
-      <c r="K51" s="36">
-        <v>0</v>
+      <c r="K51" s="18">
+        <v>7500</v>
       </c>
       <c r="L51" s="9"/>
       <c r="M51" s="10"/>
@@ -3511,10 +3517,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>31</v>
@@ -3553,7 +3559,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>30</v>
@@ -3589,16 +3595,16 @@
       <c r="P53" s="11"/>
       <c r="Q53" s="12"/>
     </row>
-    <row r="54" spans="1:17" s="13" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="47">
+    <row r="54" spans="1:17" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A54" s="46">
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D54" s="7" t="s">
         <v>31</v>
@@ -3631,16 +3637,16 @@
       <c r="P54" s="11"/>
       <c r="Q54" s="12"/>
     </row>
-    <row r="55" spans="1:17" s="13" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" s="13" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <f t="shared" si="1"/>
         <v>54</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D55" s="7" t="s">
         <v>31</v>
@@ -3667,7 +3673,7 @@
         <v>2500</v>
       </c>
       <c r="L55" s="24" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="M55" s="10"/>
       <c r="N55" s="11"/>
@@ -3681,10 +3687,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D56" s="7" t="s">
         <v>31</v>
@@ -3711,7 +3717,7 @@
         <v>0</v>
       </c>
       <c r="L56" s="24" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="M56" s="10"/>
       <c r="N56" s="11"/>
@@ -3719,22 +3725,22 @@
       <c r="P56" s="11"/>
       <c r="Q56" s="12"/>
     </row>
-    <row r="57" spans="1:17" s="13" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
         <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D57" s="7" t="s">
         <v>31</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F57" s="8">
         <v>0</v>
@@ -3767,7 +3773,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="40" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C58" s="40"/>
       <c r="D58" s="41"/>
@@ -3780,7 +3786,7 @@
       <c r="K58" s="36">
         <v>0</v>
       </c>
-      <c r="L58" s="44"/>
+      <c r="L58" s="43"/>
       <c r="M58" s="10"/>
       <c r="N58" s="11"/>
       <c r="O58" s="11"/>
@@ -3793,7 +3799,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="40" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C59" s="40"/>
       <c r="D59" s="41"/>
@@ -3806,7 +3812,7 @@
       <c r="K59" s="36">
         <v>0</v>
       </c>
-      <c r="L59" s="44"/>
+      <c r="L59" s="43"/>
       <c r="M59" s="10"/>
       <c r="N59" s="11"/>
       <c r="O59" s="11"/>
@@ -3819,11 +3825,11 @@
         <v>59</v>
       </c>
       <c r="B60" s="40" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C60" s="40"/>
       <c r="D60" s="41"/>
-      <c r="E60" s="45"/>
+      <c r="E60" s="44"/>
       <c r="F60" s="38"/>
       <c r="G60" s="38"/>
       <c r="H60" s="38"/>
@@ -3832,7 +3838,7 @@
       <c r="K60" s="36">
         <v>0</v>
       </c>
-      <c r="L60" s="44"/>
+      <c r="L60" s="43"/>
       <c r="M60" s="10"/>
       <c r="N60" s="11"/>
       <c r="O60" s="11"/>
@@ -3881,22 +3887,22 @@
       <c r="P61" s="11"/>
       <c r="Q61" s="12"/>
     </row>
-    <row r="62" spans="1:17" s="13" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <f t="shared" si="1"/>
         <v>61</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="D62" s="48" t="s">
+        <v>161</v>
+      </c>
+      <c r="D62" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="E62" s="48" t="s">
-        <v>102</v>
+      <c r="E62" s="47" t="s">
+        <v>100</v>
       </c>
       <c r="F62" s="16">
         <v>0</v>
@@ -3923,7 +3929,7 @@
       <c r="P62" s="11"/>
       <c r="Q62" s="12"/>
     </row>
-    <row r="63" spans="1:17" s="13" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
         <f t="shared" si="1"/>
         <v>62</v>
@@ -3965,7 +3971,7 @@
       <c r="P63" s="11"/>
       <c r="Q63" s="12"/>
     </row>
-    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <f t="shared" si="1"/>
         <v>63</v>
@@ -4008,7 +4014,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>77</v>
@@ -4034,45 +4040,45 @@
       <c r="J65" s="36">
         <v>0</v>
       </c>
-      <c r="K65" s="36">
-        <v>0</v>
+      <c r="K65" s="18">
+        <v>2500</v>
       </c>
       <c r="L65" s="9"/>
     </row>
-    <row r="66" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="55">
+    <row r="66" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A66" s="54">
         <f t="shared" si="1"/>
         <v>65</v>
       </c>
-      <c r="B66" s="54" t="s">
-        <v>200</v>
-      </c>
-      <c r="C66" s="54" t="s">
-        <v>163</v>
-      </c>
-      <c r="D66" s="55" t="s">
+      <c r="B66" s="53" t="s">
+        <v>198</v>
+      </c>
+      <c r="C66" s="53" t="s">
+        <v>161</v>
+      </c>
+      <c r="D66" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="E66" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="F66" s="56" t="s">
-        <v>157</v>
-      </c>
-      <c r="G66" s="56" t="s">
-        <v>157</v>
-      </c>
-      <c r="H66" s="56" t="s">
-        <v>157</v>
-      </c>
-      <c r="I66" s="56" t="s">
-        <v>157</v>
-      </c>
-      <c r="J66" s="56"/>
+      <c r="E66" s="54" t="s">
+        <v>100</v>
+      </c>
+      <c r="F66" s="55" t="s">
+        <v>155</v>
+      </c>
+      <c r="G66" s="55" t="s">
+        <v>155</v>
+      </c>
+      <c r="H66" s="55" t="s">
+        <v>155</v>
+      </c>
+      <c r="I66" s="55" t="s">
+        <v>155</v>
+      </c>
+      <c r="J66" s="55"/>
       <c r="K66" s="8">
         <v>1500</v>
       </c>
-      <c r="L66" s="50"/>
+      <c r="L66" s="49"/>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
@@ -4080,10 +4086,10 @@
         <v>66</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D67" s="7" t="s">
         <v>50</v>
@@ -4117,10 +4123,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D68" s="7" t="s">
         <v>50</v>
@@ -4148,8 +4154,8 @@
       </c>
       <c r="L68" s="24"/>
     </row>
-    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="46">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A69" s="45">
         <f t="shared" si="2"/>
         <v>68</v>
       </c>
@@ -4157,7 +4163,7 @@
         <v>61</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D69" s="7" t="s">
         <v>11</v>
@@ -4185,7 +4191,7 @@
       </c>
       <c r="L69" s="9"/>
     </row>
-    <row r="70" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <f t="shared" si="2"/>
         <v>69</v>
@@ -4221,7 +4227,7 @@
         <v>7500</v>
       </c>
       <c r="L70" s="9" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -4276,7 +4282,7 @@
         <v>11</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F72" s="8">
         <v>10000</v>
@@ -4304,7 +4310,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>19</v>
@@ -4313,7 +4319,7 @@
         <v>11</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F73" s="8"/>
       <c r="G73" s="20"/>
@@ -4362,7 +4368,7 @@
       </c>
       <c r="L74" s="9"/>
     </row>
-    <row r="75" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
         <f t="shared" si="2"/>
         <v>74</v>
@@ -4399,13 +4405,13 @@
       </c>
       <c r="L75" s="9"/>
     </row>
-    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>28</v>
@@ -4553,7 +4559,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="40" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C80" s="40"/>
       <c r="D80" s="41"/>
@@ -4574,28 +4580,28 @@
         <v>80</v>
       </c>
       <c r="B81" s="40" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C81" s="40" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D81" s="41" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E81" s="41" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F81" s="38" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G81" s="38" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H81" s="42" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I81" s="42" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="J81" s="42"/>
       <c r="K81" s="36">
@@ -4609,7 +4615,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="40" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C82" s="40"/>
       <c r="D82" s="41"/>
@@ -4624,7 +4630,7 @@
       </c>
       <c r="L82" s="42"/>
     </row>
-    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
         <f t="shared" si="2"/>
         <v>82</v>
@@ -4667,10 +4673,10 @@
         <v>83</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D84" s="7" t="s">
         <v>11</v>
@@ -4689,14 +4695,14 @@
       <c r="J84" s="9">
         <v>12500</v>
       </c>
-      <c r="K84" s="36">
-        <v>0</v>
+      <c r="K84" s="18">
+        <v>2500</v>
       </c>
       <c r="L84" s="9" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
         <f t="shared" si="2"/>
         <v>84</v>
@@ -4732,7 +4738,7 @@
         <v>2500</v>
       </c>
       <c r="L85" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="86" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -4772,7 +4778,7 @@
       </c>
       <c r="L86" s="9"/>
     </row>
-    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
         <f t="shared" si="2"/>
         <v>86</v>
@@ -4808,7 +4814,7 @@
         <v>2500</v>
       </c>
       <c r="L87" s="9" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -4816,37 +4822,21 @@
         <f t="shared" si="2"/>
         <v>87</v>
       </c>
-      <c r="B88" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D88" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E88" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F88" s="8">
-        <v>7500</v>
-      </c>
-      <c r="G88" s="8">
-        <v>2500</v>
-      </c>
-      <c r="H88" s="9">
-        <v>2500</v>
-      </c>
-      <c r="I88" s="9">
-        <v>7500</v>
-      </c>
-      <c r="J88" s="35">
-        <v>0</v>
-      </c>
+      <c r="B88" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="C88" s="40"/>
+      <c r="D88" s="41"/>
+      <c r="E88" s="41"/>
+      <c r="F88" s="38"/>
+      <c r="G88" s="38"/>
+      <c r="H88" s="42"/>
+      <c r="I88" s="42"/>
+      <c r="J88" s="42"/>
       <c r="K88" s="36">
         <v>0</v>
       </c>
-      <c r="L88" s="9"/>
+      <c r="L88" s="42"/>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" s="5">
@@ -4854,7 +4844,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>10</v>
@@ -4885,16 +4875,16 @@
       </c>
       <c r="L89" s="9"/>
     </row>
-    <row r="90" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
         <f t="shared" si="2"/>
         <v>89</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D90" s="7" t="s">
         <v>11</v>
@@ -4928,10 +4918,10 @@
         <v>90</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>11</v>
@@ -4963,16 +4953,16 @@
         <v>91</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F92" s="20"/>
       <c r="G92" s="20"/>
@@ -4988,22 +4978,22 @@
       </c>
       <c r="L92" s="24"/>
     </row>
-    <row r="93" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
         <f t="shared" si="2"/>
         <v>92</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D93" s="7" t="s">
         <v>11</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F93" s="20">
         <v>0</v>
@@ -5024,7 +5014,7 @@
         <v>1500</v>
       </c>
       <c r="L93" s="9" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="45" x14ac:dyDescent="0.25">
@@ -5036,13 +5026,13 @@
         <v>24</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D94" s="7" t="s">
         <v>11</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F94" s="20">
         <v>0</v>
@@ -5070,16 +5060,16 @@
         <v>94</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D95" s="7" t="s">
         <v>11</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F95" s="20">
         <v>0</v>
@@ -5106,26 +5096,26 @@
         <f t="shared" si="2"/>
         <v>95</v>
       </c>
-      <c r="B96" s="53" t="s">
-        <v>177</v>
-      </c>
-      <c r="C96" s="54" t="s">
-        <v>178</v>
-      </c>
-      <c r="D96" s="55" t="s">
+      <c r="B96" s="52" t="s">
+        <v>175</v>
+      </c>
+      <c r="C96" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="D96" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="E96" s="55" t="s">
+      <c r="E96" s="54" t="s">
         <v>12</v>
       </c>
       <c r="F96" s="17" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G96" s="17" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H96" s="17" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I96" s="16">
         <v>2500</v>
@@ -5144,13 +5134,13 @@
         <v>96</v>
       </c>
       <c r="B97" s="15" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C97" s="6"/>
-      <c r="D97" s="48" t="s">
+      <c r="D97" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="E97" s="48" t="s">
+      <c r="E97" s="47" t="s">
         <v>12</v>
       </c>
       <c r="F97" s="17">
@@ -5173,18 +5163,18 @@
       </c>
       <c r="L97" s="9"/>
     </row>
-    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="5">
         <f t="shared" si="2"/>
         <v>97</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C98" s="6"/>
-      <c r="D98" s="48"/>
-      <c r="E98" s="48" t="s">
-        <v>102</v>
+      <c r="D98" s="47"/>
+      <c r="E98" s="47" t="s">
+        <v>100</v>
       </c>
       <c r="F98" s="17">
         <v>0</v>
@@ -5206,15 +5196,15 @@
       </c>
       <c r="L98" s="9"/>
     </row>
-    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
         <f t="shared" si="2"/>
         <v>98</v>
       </c>
       <c r="B99" s="15"/>
       <c r="C99" s="6"/>
-      <c r="D99" s="48"/>
-      <c r="E99" s="48"/>
+      <c r="D99" s="47"/>
+      <c r="E99" s="47"/>
       <c r="F99" s="16"/>
       <c r="G99" s="16"/>
       <c r="H99" s="16"/>
@@ -5225,7 +5215,7 @@
     </row>
     <row r="101" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C101" s="27" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D101" s="28"/>
       <c r="E101" s="28"/>
@@ -5250,7 +5240,7 @@
     <row r="103" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D103" s="28"/>
       <c r="E103" s="30" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F103" s="32">
         <f>COUNTIFS(E2:E98, "House", F2:F98, "&lt;&gt;0")</f>
@@ -5274,29 +5264,29 @@
       </c>
       <c r="K103" s="32">
         <f>COUNTIFS(E2:E98, "House", K2:K98, "&lt;&gt;0")</f>
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="104" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D104" s="28"/>
       <c r="E104" s="30" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F104" s="32">
         <f>COUNTIFS(E2:E98, "Apartment", F2:F98, "&lt;&gt;0")</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G104" s="32">
         <f>COUNTIFS(E2:E98, "Apartment", G2:G98, "&lt;&gt;0")</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H104" s="32">
         <f>COUNTIFS(E2:E98, "Apartment", H2:H98, "&lt;&gt;0")</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I104" s="32">
         <f>COUNTIFS(E2:E98, "Apartment", I2:I98, "&lt;&gt;0")</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J104" s="32">
         <f>COUNTIFS(E2:E98, "Apartment", J2:J98, "&lt;&gt;0")</f>
@@ -5310,31 +5300,31 @@
     <row r="105" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D105" s="28"/>
       <c r="E105" s="30" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F105" s="32">
         <f>COUNTIFS(E2:E98, "Ind. Apartment", F2:F98, "&lt;&gt;0")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G105" s="32">
         <f>COUNTIFS(E2:E98, "Ind. Apartment", G2:G98, "&lt;&gt;0.00")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H105" s="32">
         <f>COUNTIFS(E2:E98, "Ind. Apartment", H2:H98, "&lt;&gt;0")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I105" s="32">
         <f>COUNTIFS(E2:E98, "Ind. Apartment", I2:I98, "&lt;&gt;0")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J105" s="32">
         <f>COUNTIFS(E2:E98, "Ind. Apartment", J2:J98, "&lt;&gt;0")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K105" s="32">
         <f>COUNTIFS(E2:E98, "Ind. Apartment", K2:K98, "&lt;&gt;0")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="106" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
@@ -5350,7 +5340,7 @@
     </row>
     <row r="108" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C108" s="31" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L108" s="37"/>
     </row>
@@ -5383,7 +5373,7 @@
       </c>
       <c r="K110" s="32">
         <f>COUNTIFS(D2:D98, "1st Main", K2:K98, "&lt;&gt;0")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
@@ -5412,7 +5402,7 @@
       </c>
       <c r="K111" s="32">
         <f>COUNTIFS(D2:D98, "2nd Main", K2:K98, "&lt;&gt;0")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="112" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
@@ -5441,7 +5431,7 @@
       </c>
       <c r="K112" s="32">
         <f>COUNTIFS(D2:D98, "3rd Main", K2:K98, "&lt;&gt;0")</f>
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113" spans="5:11" ht="18.75" x14ac:dyDescent="0.3">
@@ -5528,7 +5518,7 @@
       </c>
       <c r="K115" s="32">
         <f>COUNTIFS(D2:D98, "3rd Cross", K2:K98, "&lt;&gt;0")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="5:11" ht="18.75" x14ac:dyDescent="0.3">
@@ -5582,20 +5572,15 @@
       </c>
       <c r="J117" s="32">
         <f>COUNTIFS(D2:D98, "Seethammal Road", J2:J98, "&lt;&gt;0")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K117" s="32">
         <f>COUNTIFS(D2:D98, "Seethammal Road", K2:K98, "&lt;&gt;0")</f>
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L99">
-    <filterColumn colId="10">
-      <filters>
-        <filter val="0.00"/>
-      </filters>
-    </filterColumn>
     <sortState ref="A2:J96">
       <sortCondition ref="D1:D96"/>
     </sortState>

--- a/scra/scra_pymt_history_from_2021.xlsx
+++ b/scra/scra_pymt_history_from_2021.xlsx
@@ -190,9 +190,6 @@
     <t>K Bapiah</t>
   </si>
   <si>
-    <t>K Suryanarayanan</t>
-  </si>
-  <si>
     <t>Lakshmi Apartments
 37 Seethammalroad
 9840566300</t>
@@ -516,9 +513,6 @@
     <t>1 Crescent Street</t>
   </si>
   <si>
-    <t>Nirmala Rajasekar</t>
-  </si>
-  <si>
     <t>9/5 3rd Cross Street
 Aster Apartment</t>
   </si>
@@ -805,6 +799,14 @@
   </si>
   <si>
     <t>First payment in 2026</t>
+  </si>
+  <si>
+    <t>K Suryanarayanan
+Balaji   85110 30762</t>
+  </si>
+  <si>
+    <t>Nirmala Rajasekar
+Now Geetha Shankar</t>
   </si>
 </sst>
 </file>
@@ -1384,7 +1386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q117"/>
@@ -1426,19 +1428,19 @@
         <v>7</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="L1" s="24" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1479,7 +1481,7 @@
       <c r="P2" s="11"/>
       <c r="Q2" s="12"/>
     </row>
-    <row r="3" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" s="13" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <f t="shared" ref="A3:A34" si="0">A2+1</f>
         <v>2</v>
@@ -1515,7 +1517,7 @@
         <v>7500</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="M3" s="10"/>
       <c r="N3" s="11"/>
@@ -1523,16 +1525,16 @@
       <c r="P3" s="11"/>
       <c r="Q3" s="12"/>
     </row>
-    <row r="4" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" s="13" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>71</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>72</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>41</v>
@@ -1559,23 +1561,23 @@
         <v>2500</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="M4" s="10"/>
       <c r="N4" s="11"/>
       <c r="O4" s="11"/>
       <c r="Q4" s="12"/>
     </row>
-    <row r="5" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>41</v>
@@ -1611,10 +1613,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>83</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>41</v>
@@ -1647,22 +1649,22 @@
       <c r="P6" s="11"/>
       <c r="Q6" s="12"/>
     </row>
-    <row r="7" spans="1:17" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" s="13" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>41</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F7" s="20">
         <v>0</v>
@@ -1683,7 +1685,7 @@
         <v>2500</v>
       </c>
       <c r="L7" s="48" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="11"/>
@@ -1691,13 +1693,13 @@
       <c r="P7" s="11"/>
       <c r="Q7" s="12"/>
     </row>
-    <row r="8" spans="1:17" s="13" customFormat="1" ht="32.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" s="13" customFormat="1" ht="32.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>22</v>
@@ -1739,10 +1741,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>60</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>23</v>
@@ -1775,16 +1777,16 @@
       <c r="P9" s="11"/>
       <c r="Q9" s="12"/>
     </row>
-    <row r="10" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>62</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>63</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>23</v>
@@ -1815,16 +1817,16 @@
       <c r="P10" s="11"/>
       <c r="Q10" s="12"/>
     </row>
-    <row r="11" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="46">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>23</v>
@@ -1857,16 +1859,16 @@
       <c r="P11" s="11"/>
       <c r="Q11" s="12"/>
     </row>
-    <row r="12" spans="1:17" s="13" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" s="13" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>23</v>
@@ -1893,7 +1895,7 @@
         <v>2500</v>
       </c>
       <c r="L12" s="24" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="11"/>
@@ -1901,13 +1903,13 @@
       <c r="P12" s="11"/>
       <c r="Q12" s="12"/>
     </row>
-    <row r="13" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" s="13" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>20</v>
@@ -1937,7 +1939,7 @@
         <v>2500</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="M13" s="10"/>
       <c r="N13" s="11"/>
@@ -1951,7 +1953,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>20</v>
@@ -1981,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="25" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M14" s="10"/>
       <c r="N14" s="11"/>
@@ -1989,34 +1991,34 @@
       <c r="P14" s="11"/>
       <c r="Q14" s="12"/>
     </row>
-    <row r="15" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" s="13" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="50">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B15" s="51" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C15" s="51" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D15" s="47" t="s">
         <v>34</v>
       </c>
       <c r="E15" s="47" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J15" s="9">
         <v>1500</v>
@@ -2031,22 +2033,22 @@
       <c r="P15" s="11"/>
       <c r="Q15" s="12"/>
     </row>
-    <row r="16" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="50">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B16" s="51" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D16" s="47" t="s">
         <v>34</v>
       </c>
       <c r="E16" s="47" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
@@ -2071,16 +2073,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="51" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C17" s="51" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D17" s="47" t="s">
         <v>34</v>
       </c>
       <c r="E17" s="47" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
@@ -2105,7 +2107,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>20</v>
@@ -2147,10 +2149,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>21</v>
@@ -2189,16 +2191,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="51" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C20" s="51" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D20" s="47" t="s">
         <v>34</v>
       </c>
       <c r="E20" s="47" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
@@ -2247,7 +2249,7 @@
         <v>1500</v>
       </c>
       <c r="J21" s="18" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="K21" s="36">
         <v>0</v>
@@ -2259,16 +2261,16 @@
       <c r="P21" s="11"/>
       <c r="Q21" s="12"/>
     </row>
-    <row r="22" spans="1:17" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" s="13" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B22" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="6" t="s">
         <v>69</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>70</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>34</v>
@@ -2295,7 +2297,7 @@
         <v>2500</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="M22" s="10"/>
       <c r="N22" s="11"/>
@@ -2309,16 +2311,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>34</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F23" s="8">
         <v>0</v>
@@ -2345,16 +2347,16 @@
       <c r="P23" s="11"/>
       <c r="Q23" s="12"/>
     </row>
-    <row r="24" spans="1:17" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" s="13" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>102</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>34</v>
@@ -2387,22 +2389,22 @@
       <c r="P24" s="11"/>
       <c r="Q24" s="12"/>
     </row>
-    <row r="25" spans="1:17" s="13" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" s="13" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D25" s="7" t="s">
         <v>34</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F25" s="8">
         <v>0</v>
@@ -2419,7 +2421,7 @@
       <c r="J25" s="20">
         <v>0</v>
       </c>
-      <c r="K25" s="36">
+      <c r="K25" s="18">
         <v>1500</v>
       </c>
       <c r="L25" s="24"/>
@@ -2429,16 +2431,16 @@
       <c r="P25" s="11"/>
       <c r="Q25" s="12"/>
     </row>
-    <row r="26" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>34</v>
@@ -2513,16 +2515,16 @@
       <c r="P27" s="11"/>
       <c r="Q27" s="12"/>
     </row>
-    <row r="28" spans="1:17" s="13" customFormat="1" ht="32.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" s="13" customFormat="1" ht="32.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="B28" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>17</v>
@@ -2555,16 +2557,16 @@
       <c r="P28" s="11"/>
       <c r="Q28" s="12"/>
     </row>
-    <row r="29" spans="1:17" s="13" customFormat="1" ht="32.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" s="13" customFormat="1" ht="32.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>17</v>
@@ -2603,10 +2605,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="51" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C30" s="51" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D30" s="47" t="s">
         <v>11</v>
@@ -2637,16 +2639,16 @@
       <c r="P30" s="11"/>
       <c r="Q30" s="12"/>
     </row>
-    <row r="31" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" s="13" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>17</v>
@@ -2673,7 +2675,7 @@
         <v>2500</v>
       </c>
       <c r="L31" s="24" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="M31" s="10"/>
       <c r="N31" s="11"/>
@@ -2681,22 +2683,22 @@
       <c r="P31" s="11"/>
       <c r="Q31" s="12"/>
     </row>
-    <row r="32" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" s="13" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="B32" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C32" s="6" t="s">
         <v>110</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>111</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F32" s="8">
         <v>0</v>
@@ -2729,16 +2731,16 @@
         <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C33" s="6" t="s">
         <v>113</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>114</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F33" s="8">
         <v>0</v>
@@ -2765,22 +2767,22 @@
       <c r="P33" s="11"/>
       <c r="Q33" s="12"/>
     </row>
-    <row r="34" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" s="13" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>116</v>
+        <v>206</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F34" s="8">
         <v>0</v>
@@ -2797,8 +2799,8 @@
       <c r="J34" s="8">
         <v>1500</v>
       </c>
-      <c r="K34" s="36">
-        <v>0</v>
+      <c r="K34" s="18">
+        <v>1500</v>
       </c>
       <c r="L34" s="24"/>
       <c r="M34" s="10"/>
@@ -2807,22 +2809,22 @@
       <c r="P34" s="11"/>
       <c r="Q34" s="12"/>
     </row>
-    <row r="35" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" s="13" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <f t="shared" ref="A35:A66" si="1">A34+1</f>
         <v>34</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F35" s="8">
         <v>0</v>
@@ -2855,16 +2857,16 @@
         <v>35</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F36" s="8">
         <v>0</v>
@@ -2891,16 +2893,16 @@
       <c r="P36" s="11"/>
       <c r="Q36" s="12"/>
     </row>
-    <row r="37" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="50">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
       <c r="B37" s="51" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C37" s="51" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D37" s="47" t="s">
         <v>23</v>
@@ -2967,7 +2969,7 @@
         <v>0</v>
       </c>
       <c r="L38" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="M38" s="10"/>
       <c r="N38" s="11"/>
@@ -2975,7 +2977,7 @@
       <c r="P38" s="11"/>
       <c r="Q38" s="12"/>
     </row>
-    <row r="39" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" s="13" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <f t="shared" si="1"/>
         <v>38</v>
@@ -3011,7 +3013,7 @@
         <v>2500</v>
       </c>
       <c r="L39" s="9" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="M39" s="10"/>
       <c r="N39" s="11"/>
@@ -3055,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="L40" s="9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="M40" s="10"/>
       <c r="N40" s="11"/>
@@ -3063,13 +3065,13 @@
       <c r="P40" s="11"/>
       <c r="Q40" s="12"/>
     </row>
-    <row r="41" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" s="13" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="56">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="B41" s="56" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C41" s="49" t="s">
         <v>19</v>
@@ -3078,7 +3080,7 @@
         <v>11</v>
       </c>
       <c r="E41" s="56" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F41" s="8"/>
       <c r="G41" s="8"/>
@@ -3089,7 +3091,7 @@
         <v>1500</v>
       </c>
       <c r="L41" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="M41" s="10"/>
       <c r="N41" s="11"/>
@@ -3097,16 +3099,16 @@
       <c r="P41" s="11"/>
       <c r="Q41" s="12"/>
     </row>
-    <row r="42" spans="1:17" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" s="13" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="54">
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
       <c r="B42" s="54" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C42" s="53" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D42" s="54" t="s">
         <v>11</v>
@@ -3137,10 +3139,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C43" s="6" t="s">
         <v>65</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>66</v>
       </c>
       <c r="D43" s="7" t="s">
         <v>31</v>
@@ -3163,8 +3165,8 @@
       <c r="J43" s="9">
         <v>7500</v>
       </c>
-      <c r="K43" s="36">
-        <v>0</v>
+      <c r="K43" s="18">
+        <v>7500</v>
       </c>
       <c r="L43" s="9"/>
       <c r="M43" s="10"/>
@@ -3179,10 +3181,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C44" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>68</v>
       </c>
       <c r="D44" s="7" t="s">
         <v>31</v>
@@ -3215,13 +3217,13 @@
       <c r="P44" s="11"/>
       <c r="Q44" s="12"/>
     </row>
-    <row r="45" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" s="13" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <f t="shared" si="1"/>
         <v>44</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>30</v>
@@ -3251,7 +3253,7 @@
         <v>2500</v>
       </c>
       <c r="L45" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="M45" s="10"/>
       <c r="N45" s="11"/>
@@ -3259,16 +3261,16 @@
       <c r="P45" s="11"/>
       <c r="Q45" s="12"/>
     </row>
-    <row r="46" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>31</v>
@@ -3307,10 +3309,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C47" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>88</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>31</v>
@@ -3343,16 +3345,16 @@
       <c r="P47" s="11"/>
       <c r="Q47" s="12"/>
     </row>
-    <row r="48" spans="1:17" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" s="13" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <f t="shared" si="1"/>
         <v>47</v>
       </c>
       <c r="B48" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C48" s="6" t="s">
         <v>89</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>90</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>31</v>
@@ -3375,8 +3377,8 @@
       <c r="J48" s="9">
         <v>2500</v>
       </c>
-      <c r="K48" s="36">
-        <v>0</v>
+      <c r="K48" s="18">
+        <v>2500</v>
       </c>
       <c r="L48" s="9"/>
       <c r="M48" s="10"/>
@@ -3385,16 +3387,16 @@
       <c r="P48" s="11"/>
       <c r="Q48" s="12"/>
     </row>
-    <row r="49" spans="1:17" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" s="13" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
       <c r="B49" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C49" s="6" t="s">
         <v>92</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>93</v>
       </c>
       <c r="D49" s="7" t="s">
         <v>31</v>
@@ -3417,8 +3419,8 @@
       <c r="J49" s="9">
         <v>2500</v>
       </c>
-      <c r="K49" s="36">
-        <v>0</v>
+      <c r="K49" s="18">
+        <v>2500</v>
       </c>
       <c r="L49" s="9"/>
       <c r="M49" s="10"/>
@@ -3433,10 +3435,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C50" s="6" t="s">
         <v>94</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>95</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>31</v>
@@ -3469,13 +3471,13 @@
       <c r="P50" s="11"/>
       <c r="Q50" s="12"/>
     </row>
-    <row r="51" spans="1:17" s="13" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" s="13" customFormat="1" ht="56.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>30</v>
@@ -3517,10 +3519,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C52" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>31</v>
@@ -3559,7 +3561,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>30</v>
@@ -3595,16 +3597,16 @@
       <c r="P53" s="11"/>
       <c r="Q53" s="12"/>
     </row>
-    <row r="54" spans="1:17" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" s="13" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="46">
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D54" s="7" t="s">
         <v>31</v>
@@ -3637,16 +3639,16 @@
       <c r="P54" s="11"/>
       <c r="Q54" s="12"/>
     </row>
-    <row r="55" spans="1:17" s="13" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" s="13" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <f t="shared" si="1"/>
         <v>54</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D55" s="7" t="s">
         <v>31</v>
@@ -3673,7 +3675,7 @@
         <v>2500</v>
       </c>
       <c r="L55" s="24" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M55" s="10"/>
       <c r="N55" s="11"/>
@@ -3687,10 +3689,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D56" s="7" t="s">
         <v>31</v>
@@ -3717,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="L56" s="24" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="M56" s="10"/>
       <c r="N56" s="11"/>
@@ -3725,22 +3727,22 @@
       <c r="P56" s="11"/>
       <c r="Q56" s="12"/>
     </row>
-    <row r="57" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" s="13" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
         <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D57" s="7" t="s">
         <v>31</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F57" s="8">
         <v>0</v>
@@ -3773,7 +3775,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="40" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C58" s="40"/>
       <c r="D58" s="41"/>
@@ -3799,7 +3801,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="40" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C59" s="40"/>
       <c r="D59" s="41"/>
@@ -3825,7 +3827,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="40" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C60" s="40"/>
       <c r="D60" s="41"/>
@@ -3851,13 +3853,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C61" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="D61" s="7" t="s">
         <v>57</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="E61" s="7" t="s">
         <v>12</v>
@@ -3887,22 +3889,22 @@
       <c r="P61" s="11"/>
       <c r="Q61" s="12"/>
     </row>
-    <row r="62" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" s="13" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <f t="shared" si="1"/>
         <v>61</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D62" s="47" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E62" s="47" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F62" s="16">
         <v>0</v>
@@ -3929,19 +3931,19 @@
       <c r="P62" s="11"/>
       <c r="Q62" s="12"/>
     </row>
-    <row r="63" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" s="13" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
         <f t="shared" si="1"/>
         <v>62</v>
       </c>
       <c r="B63" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C63" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="D63" s="7" t="s">
         <v>49</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>50</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>12</v>
@@ -3971,19 +3973,19 @@
       <c r="P63" s="11"/>
       <c r="Q63" s="12"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>12</v>
@@ -4008,19 +4010,19 @@
       </c>
       <c r="L64" s="9"/>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E65" s="7" t="s">
         <v>12</v>
@@ -4045,34 +4047,34 @@
       </c>
       <c r="L65" s="9"/>
     </row>
-    <row r="66" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="54">
         <f t="shared" si="1"/>
         <v>65</v>
       </c>
       <c r="B66" s="53" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C66" s="53" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D66" s="54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E66" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F66" s="55" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G66" s="55" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H66" s="55" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="I66" s="55" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J66" s="55"/>
       <c r="K66" s="8">
@@ -4086,13 +4088,13 @@
         <v>66</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E67" s="7" t="s">
         <v>12</v>
@@ -4123,13 +4125,13 @@
         <v>67</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E68" s="7" t="s">
         <v>12</v>
@@ -4154,16 +4156,16 @@
       </c>
       <c r="L68" s="24"/>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="45">
         <f t="shared" si="2"/>
         <v>68</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D69" s="7" t="s">
         <v>11</v>
@@ -4191,7 +4193,7 @@
       </c>
       <c r="L69" s="9"/>
     </row>
-    <row r="70" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <f t="shared" si="2"/>
         <v>69</v>
@@ -4227,10 +4229,10 @@
         <v>7500</v>
       </c>
       <c r="L70" s="9" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
         <f t="shared" si="2"/>
         <v>70</v>
@@ -4282,7 +4284,7 @@
         <v>11</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F72" s="8">
         <v>10000</v>
@@ -4310,7 +4312,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>19</v>
@@ -4319,7 +4321,7 @@
         <v>11</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F73" s="8"/>
       <c r="G73" s="20"/>
@@ -4333,7 +4335,7 @@
       </c>
       <c r="L73" s="9"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
         <f t="shared" si="2"/>
         <v>73</v>
@@ -4363,12 +4365,12 @@
       <c r="J74" s="35">
         <v>0</v>
       </c>
-      <c r="K74" s="36">
-        <v>0</v>
+      <c r="K74" s="18">
+        <v>1500</v>
       </c>
       <c r="L74" s="9"/>
     </row>
-    <row r="75" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
         <f t="shared" si="2"/>
         <v>74</v>
@@ -4405,13 +4407,13 @@
       </c>
       <c r="L75" s="9"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>28</v>
@@ -4479,16 +4481,16 @@
       </c>
       <c r="L77" s="9"/>
     </row>
-    <row r="78" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
         <f t="shared" si="2"/>
         <v>77</v>
       </c>
       <c r="B78" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C78" s="6" t="s">
         <v>45</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>46</v>
       </c>
       <c r="D78" s="7" t="s">
         <v>11</v>
@@ -4511,8 +4513,8 @@
       <c r="J78" s="18">
         <v>10000</v>
       </c>
-      <c r="K78" s="36">
-        <v>0</v>
+      <c r="K78" s="18">
+        <v>10000</v>
       </c>
       <c r="L78" s="9"/>
     </row>
@@ -4522,7 +4524,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>10</v>
@@ -4559,7 +4561,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="40" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C80" s="40"/>
       <c r="D80" s="41"/>
@@ -4580,28 +4582,28 @@
         <v>80</v>
       </c>
       <c r="B81" s="40" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C81" s="40" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D81" s="41" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E81" s="41" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F81" s="38" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G81" s="38" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H81" s="42" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="I81" s="42" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J81" s="42"/>
       <c r="K81" s="36">
@@ -4615,7 +4617,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="40" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C82" s="40"/>
       <c r="D82" s="41"/>
@@ -4630,16 +4632,16 @@
       </c>
       <c r="L82" s="42"/>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
         <f t="shared" si="2"/>
         <v>82</v>
       </c>
       <c r="B83" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C83" s="6" t="s">
         <v>52</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>53</v>
       </c>
       <c r="D83" s="7" t="s">
         <v>11</v>
@@ -4667,16 +4669,16 @@
       </c>
       <c r="L83" s="9"/>
     </row>
-    <row r="84" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
         <f t="shared" si="2"/>
         <v>83</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D84" s="7" t="s">
         <v>11</v>
@@ -4699,19 +4701,19 @@
         <v>2500</v>
       </c>
       <c r="L84" s="9" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
         <f t="shared" si="2"/>
         <v>84</v>
       </c>
       <c r="B85" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="C85" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="D85" s="7" t="s">
         <v>11</v>
@@ -4738,7 +4740,7 @@
         <v>2500</v>
       </c>
       <c r="L85" s="9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="86" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -4747,10 +4749,10 @@
         <v>85</v>
       </c>
       <c r="B86" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C86" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="D86" s="7" t="s">
         <v>11</v>
@@ -4778,13 +4780,13 @@
       </c>
       <c r="L86" s="9"/>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
         <f t="shared" si="2"/>
         <v>86</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>10</v>
@@ -4814,7 +4816,7 @@
         <v>2500</v>
       </c>
       <c r="L87" s="9" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -4823,7 +4825,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="40" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C88" s="40"/>
       <c r="D88" s="41"/>
@@ -4844,7 +4846,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>10</v>
@@ -4875,16 +4877,16 @@
       </c>
       <c r="L89" s="9"/>
     </row>
-    <row r="90" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
         <f t="shared" si="2"/>
         <v>89</v>
       </c>
       <c r="B90" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C90" s="6" t="s">
         <v>107</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>108</v>
       </c>
       <c r="D90" s="7" t="s">
         <v>11</v>
@@ -4918,10 +4920,10 @@
         <v>90</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>11</v>
@@ -4953,16 +4955,16 @@
         <v>91</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F92" s="20"/>
       <c r="G92" s="20"/>
@@ -4978,22 +4980,22 @@
       </c>
       <c r="L92" s="24"/>
     </row>
-    <row r="93" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
         <f t="shared" si="2"/>
         <v>92</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D93" s="7" t="s">
         <v>11</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F93" s="20">
         <v>0</v>
@@ -5014,7 +5016,7 @@
         <v>1500</v>
       </c>
       <c r="L93" s="9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="45" x14ac:dyDescent="0.25">
@@ -5026,13 +5028,13 @@
         <v>24</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D94" s="7" t="s">
         <v>11</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F94" s="20">
         <v>0</v>
@@ -5060,16 +5062,16 @@
         <v>94</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D95" s="7" t="s">
         <v>11</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F95" s="20">
         <v>0</v>
@@ -5097,10 +5099,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="52" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C96" s="53" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D96" s="54" t="s">
         <v>31</v>
@@ -5109,13 +5111,13 @@
         <v>12</v>
       </c>
       <c r="F96" s="17" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G96" s="17" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H96" s="17" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="I96" s="16">
         <v>2500</v>
@@ -5134,7 +5136,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="15" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C97" s="6"/>
       <c r="D97" s="47" t="s">
@@ -5163,18 +5165,18 @@
       </c>
       <c r="L97" s="9"/>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="5">
         <f t="shared" si="2"/>
         <v>97</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="47"/>
       <c r="E98" s="47" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F98" s="17">
         <v>0</v>
@@ -5196,7 +5198,7 @@
       </c>
       <c r="L98" s="9"/>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
         <f t="shared" si="2"/>
         <v>98</v>
@@ -5215,7 +5217,7 @@
     </row>
     <row r="101" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C101" s="27" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D101" s="28"/>
       <c r="E101" s="28"/>
@@ -5240,7 +5242,7 @@
     <row r="103" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D103" s="28"/>
       <c r="E103" s="30" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F103" s="32">
         <f>COUNTIFS(E2:E98, "House", F2:F98, "&lt;&gt;0")</f>
@@ -5264,13 +5266,13 @@
       </c>
       <c r="K103" s="32">
         <f>COUNTIFS(E2:E98, "House", K2:K98, "&lt;&gt;0")</f>
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="104" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D104" s="28"/>
       <c r="E104" s="30" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F104" s="32">
         <f>COUNTIFS(E2:E98, "Apartment", F2:F98, "&lt;&gt;0")</f>
@@ -5294,13 +5296,13 @@
       </c>
       <c r="K104" s="32">
         <f>COUNTIFS(E2:E98, "Apartment", K2:K98, "&lt;&gt;0")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D105" s="28"/>
       <c r="E105" s="30" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F105" s="32">
         <f>COUNTIFS(E2:E98, "Ind. Apartment", F2:F98, "&lt;&gt;0")</f>
@@ -5324,7 +5326,7 @@
       </c>
       <c r="K105" s="32">
         <f>COUNTIFS(E2:E98, "Ind. Apartment", K2:K98, "&lt;&gt;0")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="106" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
@@ -5340,7 +5342,7 @@
     </row>
     <row r="108" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C108" s="31" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L108" s="37"/>
     </row>
@@ -5431,7 +5433,7 @@
       </c>
       <c r="K112" s="32">
         <f>COUNTIFS(D2:D98, "3rd Main", K2:K98, "&lt;&gt;0")</f>
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="113" spans="5:11" ht="18.75" x14ac:dyDescent="0.3">
@@ -5518,12 +5520,12 @@
       </c>
       <c r="K115" s="32">
         <f>COUNTIFS(D2:D98, "3rd Cross", K2:K98, "&lt;&gt;0")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="116" spans="5:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E116" s="31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F116" s="32">
         <f>COUNTIFS(D2:D98, "4th Cross", F2:F98, "&lt;&gt;0")</f>
@@ -5576,11 +5578,16 @@
       </c>
       <c r="K117" s="32">
         <f>COUNTIFS(D2:D98, "Seethammal Road", K2:K98, "&lt;&gt;0")</f>
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L99">
+    <filterColumn colId="10">
+      <filters>
+        <filter val="0.00"/>
+      </filters>
+    </filterColumn>
     <sortState ref="A2:J96">
       <sortCondition ref="D1:D96"/>
     </sortState>
